--- a/docs/StructureDefinition-VitalSignsObservationSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservationSpO2.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$101</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4444" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4121" uniqueCount="634">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1695,180 +1695,11 @@
     <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/observation.html#notes) below.</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">vs-3
 </t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.id</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].id</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.extension</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].extension</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.value</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal
-</t>
-  </si>
-  <si>
-    <t>Numerical value (with implicit precision)</t>
-  </si>
-  <si>
-    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
-  </si>
-  <si>
-    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
-  </si>
-  <si>
-    <t>Precision is handled implicitly in almost all cases of measurement.</t>
-  </si>
-  <si>
-    <t>Quantity.value</t>
-  </si>
-  <si>
-    <t>SN.2  / CQ - N/A</t>
-  </si>
-  <si>
-    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
-  </si>
-  <si>
-    <t>1240: transform using Split_SpO2_value.Consentraion on GMRV VITAL MEASUREMENT - SUPPLEMENTAL O2 (#120.5-1.4) case VUID = 4500637</t>
-  </si>
-  <si>
-    <t>Vital.VitalSign.SupplementalO2</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.comparator</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].comparator</t>
-  </si>
-  <si>
-    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
-  </si>
-  <si>
-    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
-  </si>
-  <si>
-    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
-  </si>
-  <si>
-    <t>If there is no comparator, then there is no modification of the value</t>
-  </si>
-  <si>
-    <t>How the Quantity should be understood and represented.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
-  </si>
-  <si>
-    <t>Quantity.comparator</t>
-  </si>
-  <si>
-    <t>SN.1  / CQ.1</t>
-  </si>
-  <si>
-    <t>IVL properties</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.unit</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].unit</t>
-  </si>
-  <si>
-    <t>Unit representation</t>
-  </si>
-  <si>
-    <t>A human-readable form of the unit.</t>
-  </si>
-  <si>
-    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
-  </si>
-  <si>
-    <t>Quantity.unit</t>
-  </si>
-  <si>
-    <t>(see OBX.6 etc.) / CQ.2</t>
-  </si>
-  <si>
-    <t>PQ.unit</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.system</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].system</t>
-  </si>
-  <si>
-    <t>System that defines coded unit form</t>
-  </si>
-  <si>
-    <t>The identification of the system that provides the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>Need to know the system that defines the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>Quantity.system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qty-3
-</t>
-  </si>
-  <si>
-    <t>CO.codeSystem, PQ.translation.codeSystem</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]:valueQuantity.code</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x].code</t>
-  </si>
-  <si>
-    <t>Coded form of the unit</t>
-  </si>
-  <si>
-    <t>A computer processable form of the unit in some unit representation system.</t>
-  </si>
-  <si>
-    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
-  </si>
-  <si>
-    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
-  </si>
-  <si>
-    <t>Quantity.code</t>
-  </si>
-  <si>
-    <t>PQ.code, MO.currency, PQ.translation.code</t>
   </si>
   <si>
     <t>Observation.component.dataAbsentReason</t>
@@ -1935,31 +1766,169 @@
     <t>Observation.component:FlowRate.value[x]</t>
   </si>
   <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
     <t>Observation.component:FlowRate.value[x].id</t>
   </si>
   <si>
+    <t>Observation.component.value[x].id</t>
+  </si>
+  <si>
     <t>Observation.component:FlowRate.value[x].extension</t>
   </si>
   <si>
+    <t>Observation.component.value[x].extension</t>
+  </si>
+  <si>
     <t>Observation.component:FlowRate.value[x].value</t>
   </si>
   <si>
+    <t>Observation.component.value[x].value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Numerical value (with implicit precision)</t>
+  </si>
+  <si>
+    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
+  </si>
+  <si>
+    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
+  </si>
+  <si>
+    <t>Precision is handled implicitly in almost all cases of measurement.</t>
+  </si>
+  <si>
+    <t>Quantity.value</t>
+  </si>
+  <si>
+    <t>SN.2  / CQ - N/A</t>
+  </si>
+  <si>
+    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
+  </si>
+  <si>
+    <t>1239: transform using Split_SpO2_value.Flow on GMRV VITAL MEASUREMENT - SUPPLEMENTAL O2 (#120.5-1.4) case VUID = 4500637</t>
+  </si>
+  <si>
+    <t>Vital.VitalSign.SupplementalO2</t>
+  </si>
+  <si>
     <t>Observation.component:FlowRate.value[x].comparator</t>
   </si>
   <si>
+    <t>Observation.component.value[x].comparator</t>
+  </si>
+  <si>
+    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+  </si>
+  <si>
+    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
+  </si>
+  <si>
+    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
+  </si>
+  <si>
+    <t>If there is no comparator, then there is no modification of the value</t>
+  </si>
+  <si>
+    <t>How the Quantity should be understood and represented.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
+  </si>
+  <si>
+    <t>Quantity.comparator</t>
+  </si>
+  <si>
+    <t>SN.1  / CQ.1</t>
+  </si>
+  <si>
+    <t>IVL properties</t>
+  </si>
+  <si>
     <t>Observation.component:FlowRate.value[x].unit</t>
   </si>
   <si>
+    <t>Observation.component.value[x].unit</t>
+  </si>
+  <si>
+    <t>Unit representation</t>
+  </si>
+  <si>
+    <t>A human-readable form of the unit.</t>
+  </si>
+  <si>
+    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
+  </si>
+  <si>
+    <t>Quantity.unit</t>
+  </si>
+  <si>
+    <t>(see OBX.6 etc.) / CQ.2</t>
+  </si>
+  <si>
+    <t>PQ.unit</t>
+  </si>
+  <si>
     <t>Observation.component:FlowRate.value[x].system</t>
   </si>
   <si>
+    <t>Observation.component.value[x].system</t>
+  </si>
+  <si>
+    <t>System that defines coded unit form</t>
+  </si>
+  <si>
+    <t>The identification of the system that provides the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Need to know the system that defines the coded form of the unit.</t>
+  </si>
+  <si>
     <t>http://unitsofmeasure.org</t>
   </si>
   <si>
+    <t>Quantity.system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qty-3
+</t>
+  </si>
+  <si>
+    <t>CO.codeSystem, PQ.translation.codeSystem</t>
+  </si>
+  <si>
     <t>Observation.component:FlowRate.value[x].code</t>
   </si>
   <si>
+    <t>Observation.component.value[x].code</t>
+  </si>
+  <si>
+    <t>Coded form of the unit</t>
+  </si>
+  <si>
+    <t>A computer processable form of the unit in some unit representation system.</t>
+  </si>
+  <si>
+    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+  </si>
+  <si>
+    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+  </si>
+  <si>
     <t>L/min</t>
+  </si>
+  <si>
+    <t>Quantity.code</t>
+  </si>
+  <si>
+    <t>PQ.code, MO.currency, PQ.translation.code</t>
   </si>
   <si>
     <t>Observation.component:FlowRate.dataAbsentReason</t>
@@ -2010,6 +1979,9 @@
   </si>
   <si>
     <t>Observation.component:Concentration.value[x].value</t>
+  </si>
+  <si>
+    <t>1240: transform using Split_SpO2_value.Consentraion on GMRV VITAL MEASUREMENT - SUPPLEMENTAL O2 (#120.5-1.4) case VUID = 4500637</t>
   </si>
   <si>
     <t>Observation.component:Concentration.value[x].comparator</t>
@@ -2350,7 +2322,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR109"/>
+  <dimension ref="A1:AR101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.11328125" customWidth="true" bestFit="true"/>
@@ -10709,14 +10681,16 @@
         <v>84</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AC66" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
         <v>531</v>
@@ -10728,7 +10702,7 @@
         <v>94</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>106</v>
@@ -10737,7 +10711,7 @@
         <v>84</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>378</v>
@@ -10760,14 +10734,12 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>539</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>84</v>
       </c>
@@ -10785,22 +10757,22 @@
         <v>84</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="L67" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>534</v>
-      </c>
       <c r="O67" t="s" s="2">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -10828,10 +10800,10 @@
         <v>291</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -10849,7 +10821,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10858,7 +10830,7 @@
         <v>94</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>106</v>
@@ -10867,19 +10839,19 @@
         <v>84</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>537</v>
+        <v>84</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>378</v>
+        <v>137</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>380</v>
+        <v>84</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -10890,21 +10862,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>542</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>84</v>
+        <v>391</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>84</v>
@@ -10916,16 +10888,20 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>207</v>
+        <v>392</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
       </c>
@@ -10949,13 +10925,13 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>84</v>
+        <v>291</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>84</v>
+        <v>396</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>84</v>
+        <v>397</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
@@ -10973,37 +10949,37 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>209</v>
+        <v>542</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>84</v>
+        <v>398</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>84</v>
+        <v>399</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>210</v>
+        <v>400</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>84</v>
+        <v>401</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -11017,11 +10993,11 @@
         <v>543</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11040,18 +11016,20 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>141</v>
+        <v>544</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>213</v>
+        <v>545</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
       </c>
@@ -11087,19 +11065,19 @@
         <v>84</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>215</v>
+        <v>84</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>216</v>
+        <v>543</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11111,7 +11089,7 @@
         <v>84</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>84</v>
@@ -11120,10 +11098,10 @@
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>84</v>
+        <v>455</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>210</v>
+        <v>456</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>84</v>
@@ -11140,12 +11118,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C70" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>547</v>
+      </c>
       <c r="D70" t="s" s="2">
         <v>84</v>
       </c>
@@ -11157,7 +11137,7 @@
         <v>94</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>84</v>
@@ -11166,7 +11146,7 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>547</v>
+        <v>449</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>548</v>
@@ -11175,10 +11155,10 @@
         <v>549</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>550</v>
+        <v>516</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>551</v>
+        <v>517</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11227,19 +11207,19 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>552</v>
+        <v>514</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>106</v>
+        <v>519</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>84</v>
@@ -11248,10 +11228,10 @@
         <v>84</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>553</v>
+        <v>520</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>554</v>
+        <v>521</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>84</v>
@@ -11260,18 +11240,18 @@
         <v>84</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>555</v>
+        <v>84</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>556</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>558</v>
+        <v>522</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11288,30 +11268,26 @@
         <v>84</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>114</v>
+        <v>206</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>559</v>
+        <v>207</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>560</v>
+        <v>208</v>
       </c>
       <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>561</v>
-      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q71" t="s" s="2">
-        <v>562</v>
-      </c>
+      <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
         <v>84</v>
       </c>
@@ -11331,13 +11307,13 @@
         <v>84</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>183</v>
+        <v>84</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>563</v>
+        <v>84</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>564</v>
+        <v>84</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11355,7 +11331,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>565</v>
+        <v>209</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11367,7 +11343,7 @@
         <v>84</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>84</v>
@@ -11376,10 +11352,10 @@
         <v>84</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>566</v>
+        <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>567</v>
+        <v>210</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>84</v>
@@ -11396,21 +11372,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>568</v>
+        <v>551</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>569</v>
+        <v>523</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>84</v>
@@ -11419,21 +11395,21 @@
         <v>84</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>206</v>
+        <v>140</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>570</v>
+        <v>141</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>84</v>
       </c>
@@ -11481,19 +11457,19 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>573</v>
+        <v>216</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>84</v>
@@ -11502,10 +11478,10 @@
         <v>84</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>574</v>
+        <v>84</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>575</v>
+        <v>210</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>84</v>
@@ -11522,43 +11498,45 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>576</v>
+        <v>552</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>577</v>
+        <v>524</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>84</v>
+        <v>460</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J73" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>578</v>
+        <v>461</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O73" t="s" s="2">
-        <v>580</v>
+        <v>149</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>84</v>
@@ -11607,19 +11585,19 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>581</v>
+        <v>463</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>582</v>
+        <v>84</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>84</v>
@@ -11628,10 +11606,10 @@
         <v>84</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>574</v>
+        <v>84</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>583</v>
+        <v>137</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>84</v>
@@ -11648,10 +11626,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>584</v>
+        <v>553</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>585</v>
+        <v>525</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11659,13 +11637,13 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>84</v>
@@ -11674,19 +11652,19 @@
         <v>95</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>114</v>
+        <v>191</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>586</v>
+        <v>526</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>587</v>
+        <v>527</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>588</v>
+        <v>528</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>589</v>
+        <v>529</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -11696,7 +11674,7 @@
         <v>84</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>84</v>
+        <v>554</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>84</v>
@@ -11711,13 +11689,13 @@
         <v>84</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>84</v>
+        <v>291</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>84</v>
+        <v>293</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -11735,10 +11713,10 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>590</v>
+        <v>525</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>94</v>
@@ -11753,16 +11731,16 @@
         <v>84</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>84</v>
+        <v>530</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>574</v>
+        <v>296</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>591</v>
+        <v>297</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>84</v>
+        <v>298</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>84</v>
@@ -11776,10 +11754,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>592</v>
+        <v>555</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>592</v>
+        <v>531</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11799,22 +11777,22 @@
         <v>84</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>191</v>
+        <v>556</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>593</v>
+        <v>532</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>594</v>
+        <v>533</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>595</v>
+        <v>534</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
@@ -11842,10 +11820,10 @@
         <v>291</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>84</v>
@@ -11863,7 +11841,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>592</v>
+        <v>531</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11872,7 +11850,7 @@
         <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>596</v>
+        <v>535</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>106</v>
@@ -11881,19 +11859,19 @@
         <v>84</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>84</v>
+        <v>536</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>137</v>
+        <v>378</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>84</v>
+        <v>380</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
@@ -11904,21 +11882,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>597</v>
+        <v>557</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>597</v>
+        <v>558</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>391</v>
+        <v>84</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>84</v>
@@ -11930,20 +11908,16 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>392</v>
+        <v>207</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>84</v>
       </c>
@@ -11967,13 +11941,13 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>291</v>
+        <v>84</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>396</v>
+        <v>84</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>397</v>
+        <v>84</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -11991,37 +11965,37 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>597</v>
+        <v>209</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>398</v>
+        <v>84</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>399</v>
+        <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>400</v>
+        <v>210</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -12032,14 +12006,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>598</v>
+        <v>559</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>598</v>
+        <v>560</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -12058,20 +12032,18 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>599</v>
+        <v>141</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>600</v>
+        <v>213</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>84</v>
       </c>
@@ -12107,19 +12079,19 @@
         <v>84</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>84</v>
+        <v>199</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>598</v>
+        <v>216</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12131,7 +12103,7 @@
         <v>84</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>84</v>
@@ -12140,10 +12112,10 @@
         <v>84</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>455</v>
+        <v>84</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>456</v>
+        <v>210</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>84</v>
@@ -12160,20 +12132,18 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>601</v>
+        <v>561</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>602</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>94</v>
@@ -12188,19 +12158,19 @@
         <v>95</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>449</v>
+        <v>563</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>603</v>
+        <v>564</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>604</v>
+        <v>565</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>516</v>
+        <v>566</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>517</v>
+        <v>567</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12249,19 +12219,19 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>514</v>
+        <v>568</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>519</v>
+        <v>106</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>84</v>
@@ -12270,10 +12240,10 @@
         <v>84</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>520</v>
+        <v>569</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>521</v>
+        <v>570</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>84</v>
@@ -12282,18 +12252,18 @@
         <v>84</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>84</v>
+        <v>571</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>84</v>
+        <v>572</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>605</v>
+        <v>573</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>522</v>
+        <v>574</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12310,26 +12280,30 @@
         <v>84</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>206</v>
+        <v>114</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>207</v>
+        <v>575</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>208</v>
+        <v>576</v>
       </c>
       <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+      <c r="O79" t="s" s="2">
+        <v>577</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q79" s="2"/>
+      <c r="Q79" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="R79" t="s" s="2">
         <v>84</v>
       </c>
@@ -12349,13 +12323,13 @@
         <v>84</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>84</v>
+        <v>183</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>84</v>
+        <v>579</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>84</v>
+        <v>580</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>84</v>
@@ -12373,7 +12347,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>209</v>
+        <v>581</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12385,7 +12359,7 @@
         <v>84</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>84</v>
@@ -12394,10 +12368,10 @@
         <v>84</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>84</v>
+        <v>582</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>210</v>
+        <v>583</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>84</v>
@@ -12414,44 +12388,44 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>606</v>
+        <v>584</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>523</v>
+        <v>585</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>141</v>
+        <v>586</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O80" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" t="s" s="2">
+        <v>588</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
       </c>
@@ -12499,19 +12473,19 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>216</v>
+        <v>589</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>84</v>
@@ -12520,10 +12494,10 @@
         <v>84</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>84</v>
+        <v>590</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>210</v>
+        <v>591</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>84</v>
@@ -12540,52 +12514,50 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>607</v>
+        <v>592</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>524</v>
+        <v>593</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>460</v>
+        <v>84</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J81" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>461</v>
+        <v>594</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>149</v>
+        <v>596</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>84</v>
+        <v>597</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>84</v>
@@ -12627,19 +12599,19 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>463</v>
+        <v>598</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>84</v>
+        <v>599</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>84</v>
@@ -12648,10 +12620,10 @@
         <v>84</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>84</v>
+        <v>590</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>137</v>
+        <v>600</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>84</v>
@@ -12668,10 +12640,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>525</v>
+        <v>602</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12694,29 +12666,29 @@
         <v>95</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>191</v>
+        <v>114</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>526</v>
+        <v>603</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>527</v>
+        <v>604</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>528</v>
+        <v>605</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>529</v>
+        <v>606</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>84</v>
+        <v>607</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>609</v>
+        <v>84</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>84</v>
@@ -12731,13 +12703,13 @@
         <v>84</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>291</v>
+        <v>84</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>292</v>
+        <v>84</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>293</v>
+        <v>84</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>84</v>
@@ -12755,10 +12727,10 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>525</v>
+        <v>608</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>94</v>
@@ -12773,16 +12745,16 @@
         <v>84</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>530</v>
+        <v>84</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>296</v>
+        <v>590</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>297</v>
+        <v>609</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>298</v>
+        <v>84</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>84</v>
@@ -12799,7 +12771,7 @@
         <v>610</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12819,22 +12791,22 @@
         <v>84</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="L83" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>534</v>
-      </c>
       <c r="O83" t="s" s="2">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>84</v>
@@ -12862,10 +12834,10 @@
         <v>291</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>84</v>
@@ -12883,7 +12855,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -12892,7 +12864,7 @@
         <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>106</v>
@@ -12901,19 +12873,19 @@
         <v>84</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>537</v>
+        <v>84</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>378</v>
+        <v>137</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>380</v>
+        <v>84</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -12931,14 +12903,14 @@
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>84</v>
+        <v>391</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>84</v>
@@ -12950,16 +12922,20 @@
         <v>84</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>207</v>
+        <v>392</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>84</v>
       </c>
@@ -12983,13 +12959,13 @@
         <v>84</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>84</v>
+        <v>291</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>84</v>
+        <v>396</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>84</v>
+        <v>397</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>84</v>
@@ -13007,37 +12983,37 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>209</v>
+        <v>542</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>84</v>
+        <v>398</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>84</v>
+        <v>399</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>210</v>
+        <v>400</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>84</v>
+        <v>401</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13051,11 +13027,11 @@
         <v>612</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -13074,18 +13050,20 @@
         <v>84</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>141</v>
+        <v>544</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>213</v>
+        <v>545</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>84</v>
       </c>
@@ -13121,19 +13099,19 @@
         <v>84</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>215</v>
+        <v>84</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>216</v>
+        <v>543</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13145,7 +13123,7 @@
         <v>84</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>84</v>
@@ -13154,10 +13132,10 @@
         <v>84</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>84</v>
+        <v>455</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>210</v>
+        <v>456</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>84</v>
@@ -13177,15 +13155,17 @@
         <v>613</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C86" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>614</v>
+      </c>
       <c r="D86" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>94</v>
@@ -13200,19 +13180,19 @@
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>547</v>
+        <v>449</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>548</v>
+        <v>615</v>
       </c>
       <c r="M86" t="s" s="2">
         <v>549</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>550</v>
+        <v>516</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>551</v>
+        <v>517</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>84</v>
@@ -13261,19 +13241,19 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>552</v>
+        <v>514</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>106</v>
+        <v>519</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>84</v>
@@ -13282,10 +13262,10 @@
         <v>84</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>553</v>
+        <v>520</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>554</v>
+        <v>521</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>84</v>
@@ -13302,10 +13282,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>558</v>
+        <v>522</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13322,30 +13302,26 @@
         <v>84</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>114</v>
+        <v>206</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>559</v>
+        <v>207</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>560</v>
+        <v>208</v>
       </c>
       <c r="N87" s="2"/>
-      <c r="O87" t="s" s="2">
-        <v>561</v>
-      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q87" t="s" s="2">
-        <v>562</v>
-      </c>
+      <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
         <v>84</v>
       </c>
@@ -13365,13 +13341,13 @@
         <v>84</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>183</v>
+        <v>84</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>563</v>
+        <v>84</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>564</v>
+        <v>84</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>84</v>
@@ -13389,7 +13365,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>565</v>
+        <v>209</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13401,7 +13377,7 @@
         <v>84</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>84</v>
@@ -13410,10 +13386,10 @@
         <v>84</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>566</v>
+        <v>84</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>567</v>
+        <v>210</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>84</v>
@@ -13430,44 +13406,44 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>569</v>
+        <v>523</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>206</v>
+        <v>140</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>570</v>
+        <v>141</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>84</v>
       </c>
@@ -13515,19 +13491,19 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>573</v>
+        <v>216</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>84</v>
@@ -13536,10 +13512,10 @@
         <v>84</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>574</v>
+        <v>84</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>575</v>
+        <v>210</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>84</v>
@@ -13556,50 +13532,52 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>577</v>
+        <v>524</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>84</v>
+        <v>460</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I89" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="J89" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>578</v>
+        <v>461</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O89" t="s" s="2">
-        <v>580</v>
+        <v>149</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
-        <v>617</v>
+        <v>84</v>
       </c>
       <c r="S89" t="s" s="2">
         <v>84</v>
@@ -13641,19 +13619,19 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>581</v>
+        <v>463</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>582</v>
+        <v>84</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>84</v>
@@ -13662,10 +13640,10 @@
         <v>84</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>574</v>
+        <v>84</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>583</v>
+        <v>137</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>84</v>
@@ -13682,10 +13660,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>585</v>
+        <v>525</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13708,29 +13686,29 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>114</v>
+        <v>191</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>586</v>
+        <v>526</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>587</v>
+        <v>527</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>588</v>
+        <v>528</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>589</v>
+        <v>529</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>619</v>
+        <v>84</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>84</v>
+        <v>620</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>84</v>
@@ -13745,13 +13723,13 @@
         <v>84</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>84</v>
+        <v>291</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>84</v>
+        <v>292</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>84</v>
+        <v>293</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>84</v>
@@ -13769,10 +13747,10 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>590</v>
+        <v>525</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>94</v>
@@ -13787,16 +13765,16 @@
         <v>84</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>84</v>
+        <v>530</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>574</v>
+        <v>296</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>591</v>
+        <v>297</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>84</v>
+        <v>298</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>84</v>
@@ -13810,10 +13788,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>592</v>
+        <v>531</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13833,22 +13811,22 @@
         <v>84</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>191</v>
+        <v>556</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>593</v>
+        <v>532</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>594</v>
+        <v>533</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>595</v>
+        <v>534</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
@@ -13876,10 +13854,10 @@
         <v>291</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>84</v>
@@ -13897,7 +13875,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>592</v>
+        <v>531</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -13906,7 +13884,7 @@
         <v>94</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>596</v>
+        <v>535</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>106</v>
@@ -13915,19 +13893,19 @@
         <v>84</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>84</v>
+        <v>536</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>137</v>
+        <v>378</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>84</v>
+        <v>380</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -13938,21 +13916,21 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>597</v>
+        <v>558</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>391</v>
+        <v>84</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>84</v>
@@ -13964,20 +13942,16 @@
         <v>84</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>392</v>
+        <v>207</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>84</v>
       </c>
@@ -14001,13 +13975,13 @@
         <v>84</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>291</v>
+        <v>84</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>396</v>
+        <v>84</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>397</v>
+        <v>84</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>84</v>
@@ -14025,37 +13999,37 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>597</v>
+        <v>209</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>398</v>
+        <v>84</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>399</v>
+        <v>84</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>400</v>
+        <v>210</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>
@@ -14066,14 +14040,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>598</v>
+        <v>560</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -14092,20 +14066,18 @@
         <v>84</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>599</v>
+        <v>141</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>600</v>
+        <v>213</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>84</v>
       </c>
@@ -14141,19 +14113,19 @@
         <v>84</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>84</v>
+        <v>199</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>598</v>
+        <v>216</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14165,7 +14137,7 @@
         <v>84</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>84</v>
@@ -14174,10 +14146,10 @@
         <v>84</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>455</v>
+        <v>84</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>456</v>
+        <v>210</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>84</v>
@@ -14194,20 +14166,18 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="C94" t="s" s="2">
-        <v>624</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>94</v>
@@ -14222,19 +14192,19 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>449</v>
+        <v>563</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>625</v>
+        <v>564</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>604</v>
+        <v>565</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>516</v>
+        <v>566</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>517</v>
+        <v>567</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>84</v>
@@ -14283,19 +14253,19 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>514</v>
+        <v>568</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>519</v>
+        <v>106</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>84</v>
@@ -14304,10 +14274,10 @@
         <v>84</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>520</v>
+        <v>569</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>521</v>
+        <v>570</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>84</v>
@@ -14316,10 +14286,10 @@
         <v>84</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>84</v>
+        <v>625</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>84</v>
+        <v>572</v>
       </c>
     </row>
     <row r="95" hidden="true">
@@ -14327,7 +14297,7 @@
         <v>626</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>522</v>
+        <v>574</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14344,26 +14314,30 @@
         <v>84</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>206</v>
+        <v>114</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>207</v>
+        <v>575</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>208</v>
+        <v>576</v>
       </c>
       <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
+      <c r="O95" t="s" s="2">
+        <v>577</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q95" s="2"/>
+      <c r="Q95" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="R95" t="s" s="2">
         <v>84</v>
       </c>
@@ -14383,13 +14357,13 @@
         <v>84</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>84</v>
+        <v>183</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>84</v>
+        <v>579</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>84</v>
+        <v>580</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>84</v>
@@ -14407,7 +14381,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>209</v>
+        <v>581</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -14419,7 +14393,7 @@
         <v>84</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>84</v>
@@ -14428,10 +14402,10 @@
         <v>84</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>84</v>
+        <v>582</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>210</v>
+        <v>583</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>84</v>
@@ -14451,41 +14425,41 @@
         <v>627</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>523</v>
+        <v>585</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>141</v>
+        <v>586</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" t="s" s="2">
+        <v>588</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
       </c>
@@ -14533,19 +14507,19 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>216</v>
+        <v>589</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>84</v>
@@ -14554,10 +14528,10 @@
         <v>84</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>84</v>
+        <v>590</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>210</v>
+        <v>591</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>84</v>
@@ -14577,49 +14551,47 @@
         <v>628</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>524</v>
+        <v>593</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>460</v>
+        <v>84</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J97" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>461</v>
+        <v>594</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>149</v>
+        <v>596</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>84</v>
+        <v>597</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>84</v>
@@ -14661,19 +14633,19 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>463</v>
+        <v>598</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>84</v>
+        <v>599</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>84</v>
@@ -14682,10 +14654,10 @@
         <v>84</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>84</v>
+        <v>590</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>137</v>
+        <v>600</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>84</v>
@@ -14705,7 +14677,7 @@
         <v>629</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>525</v>
+        <v>602</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14728,29 +14700,29 @@
         <v>95</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>191</v>
+        <v>114</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>526</v>
+        <v>603</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>527</v>
+        <v>604</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>528</v>
+        <v>605</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>529</v>
+        <v>606</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
-        <v>84</v>
+        <v>630</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>630</v>
+        <v>84</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>84</v>
@@ -14765,13 +14737,13 @@
         <v>84</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>291</v>
+        <v>84</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>292</v>
+        <v>84</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>293</v>
+        <v>84</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>84</v>
@@ -14789,10 +14761,10 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>525</v>
+        <v>608</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>94</v>
@@ -14807,16 +14779,16 @@
         <v>84</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>530</v>
+        <v>84</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>296</v>
+        <v>590</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>297</v>
+        <v>609</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>298</v>
+        <v>84</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>84</v>
@@ -14833,7 +14805,7 @@
         <v>631</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14853,22 +14825,22 @@
         <v>84</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="N99" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="L99" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>534</v>
-      </c>
       <c r="O99" t="s" s="2">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>84</v>
@@ -14896,10 +14868,10 @@
         <v>291</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>84</v>
@@ -14917,7 +14889,7 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
@@ -14926,7 +14898,7 @@
         <v>94</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>106</v>
@@ -14935,19 +14907,19 @@
         <v>84</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>537</v>
+        <v>84</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>378</v>
+        <v>137</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>380</v>
+        <v>84</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
@@ -14965,14 +14937,14 @@
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>84</v>
+        <v>391</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>84</v>
@@ -14984,16 +14956,20 @@
         <v>84</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>207</v>
+        <v>392</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>84</v>
       </c>
@@ -15017,13 +14993,13 @@
         <v>84</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>84</v>
+        <v>291</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>84</v>
+        <v>396</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>84</v>
+        <v>397</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>84</v>
@@ -15041,37 +15017,37 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>209</v>
+        <v>542</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>84</v>
+        <v>398</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>84</v>
+        <v>399</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>210</v>
+        <v>400</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>84</v>
+        <v>401</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15085,11 +15061,11 @@
         <v>633</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -15108,18 +15084,20 @@
         <v>84</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>141</v>
+        <v>544</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>213</v>
+        <v>545</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O101" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>84</v>
       </c>
@@ -15155,19 +15133,19 @@
         <v>84</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>214</v>
+        <v>84</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>215</v>
+        <v>84</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>199</v>
+        <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>216</v>
+        <v>543</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15179,7 +15157,7 @@
         <v>84</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>84</v>
@@ -15188,10 +15166,10 @@
         <v>84</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>84</v>
+        <v>455</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>210</v>
+        <v>456</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>84</v>
@@ -15203,1031 +15181,11 @@
         <v>84</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="P102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR102" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="103" hidden="true">
-      <c r="A103" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="P103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q103" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="R103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR103" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="P104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR104" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="105" hidden="true">
-      <c r="A105" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="P105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR105" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="106" hidden="true">
-      <c r="A106" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="P106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR106" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="107" hidden="true">
-      <c r="A107" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="P107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR107" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="108" hidden="true">
-      <c r="A108" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="P108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AQ108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR108" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="109" hidden="true">
-      <c r="A109" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="P109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR109" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR109">
+  <autoFilter ref="A1:AR101">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16237,7 +15195,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI108">
+  <conditionalFormatting sqref="A2:AI100">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-VitalSignsObservationSpO2.xlsx
+++ b/docs/StructureDefinition-VitalSignsObservationSpO2.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA GMRV VITAL MEASUREMENT (file 120.5) to FHIR Observation</t>
+    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (#120.5) to us-core-pulse-oximetry</t>
   </si>
   <si>
     <t>Purpose</t>
